--- a/api/test/import/team-sample.xlsx
+++ b/api/test/import/team-sample.xlsx
@@ -19,13 +19,13 @@
   <definedNames>
     <definedName name="YesNo">Choices!$A$2:$A$3</definedName>
     <definedName name="Days">Choices!$B$2:$B$8</definedName>
-    <definedName name="EventTypes">Choices!$C$2:$C$4</definedName>
+    <definedName name="EventTypes">Choices!$C$2:$C$5</definedName>
     <definedName name="Repeats">Choices!$D$2:$D$5</definedName>
     <definedName name="Shirts">Choices!$E$2:$E$11</definedName>
     <definedName name="RefGroups">Choices!$F$2:$F$3</definedName>
-    <definedName name="Lists">Choices!$G$2:$G$3</definedName>
+    <definedName name="Lists">Choices!$G$2:$G$4</definedName>
     <definedName name="Programs">Choices!$H$2:$H$4</definedName>
-    <definedName name="DefaultKinds">Choices!$I$2:$I$4</definedName>
+    <definedName name="DefaultKinds">Choices!$I$2:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Team'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Staff'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Roster'!$1:$1</definedName>
@@ -378,6 +378,21 @@
         <t>Blank = end of the season (June 30).</t>
       </text>
     </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Blank = weekly. Or Every 2 weeks, Every 3 weeks, or None for this one date only.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Like 3, or Courts 3-4.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Practice uniform color. New colors are added to the team's list.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -410,12 +425,22 @@
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>For team events only; tournaments don't repeat.</t>
+        <t>For practices and team events; tournaments don't repeat.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Days of the week, like 'Tue, Thu'.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Practices only.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Practices only.</t>
       </text>
     </comment>
   </commentList>
@@ -892,7 +917,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>One row per weekly practice.</t>
+          <t>One row per practice series: weekly, every 2 weeks or every 3 weeks.</t>
         </is>
       </c>
       <c r="C17" s="6">
@@ -908,7 +933,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>One row per tournament, team event or deadline.</t>
+          <t>One row per tournament, team event, deadline or one-off practice.</t>
         </is>
       </c>
       <c r="C18" s="6">
@@ -924,7 +949,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Optional: packing checklist and uniform items.</t>
+          <t>Optional: packing checklist, uniform items and practice uniform colors.</t>
         </is>
       </c>
       <c r="C19" s="6">
@@ -9414,7 +9439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9423,8 +9448,11 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -9460,10 +9488,25 @@
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
+          <t>Repeats</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Uniform color</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -9498,10 +9541,25 @@
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
           <t>A5 Sportsplex</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>Bring both jerseys</t>
         </is>
@@ -9530,10 +9588,25 @@
       <c r="F3" s="22" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
+          <t>Every 2 weeks</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
           <t>Test Gym</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -9562,12 +9635,19 @@
       <c r="F4" s="22" t="n">
         <v>46536</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Test Gym</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Both jerseys</t>
         </is>
@@ -9582,6 +9662,9 @@
       <c r="F5" s="22" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -9592,6 +9675,9 @@
       <c r="F6" s="22" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -9602,6 +9688,9 @@
       <c r="F7" s="22" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -9612,6 +9701,9 @@
       <c r="F8" s="22" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -9622,6 +9714,9 @@
       <c r="F9" s="22" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -9632,6 +9727,9 @@
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -9642,6 +9740,9 @@
       <c r="F11" s="22" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -9652,6 +9753,9 @@
       <c r="F12" s="22" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -9662,6 +9766,9 @@
       <c r="F13" s="22" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -9672,6 +9779,9 @@
       <c r="F14" s="22" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -9682,6 +9792,9 @@
       <c r="F15" s="22" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -9692,6 +9805,9 @@
       <c r="F16" s="22" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9702,6 +9818,9 @@
       <c r="F17" s="22" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -9712,6 +9831,9 @@
       <c r="F18" s="22" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -9722,6 +9844,9 @@
       <c r="F19" s="22" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -9732,6 +9857,9 @@
       <c r="F20" s="22" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9742,6 +9870,9 @@
       <c r="F21" s="22" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -9752,6 +9883,9 @@
       <c r="F22" s="22" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -9762,6 +9896,9 @@
       <c r="F23" s="22" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -9772,6 +9909,9 @@
       <c r="F24" s="22" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -9782,6 +9922,9 @@
       <c r="F25" s="22" t="n"/>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -9792,6 +9935,9 @@
       <c r="F26" s="22" t="n"/>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -9802,6 +9948,9 @@
       <c r="F27" s="22" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -9812,6 +9961,9 @@
       <c r="F28" s="22" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -9822,6 +9974,9 @@
       <c r="F29" s="22" t="n"/>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -9832,6 +9987,9 @@
       <c r="F30" s="22" t="n"/>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -9842,6 +10000,9 @@
       <c r="F31" s="22" t="n"/>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -9852,6 +10013,9 @@
       <c r="F32" s="22" t="n"/>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -9862,6 +10026,9 @@
       <c r="F33" s="22" t="n"/>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -9872,6 +10039,9 @@
       <c r="F34" s="22" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -9882,6 +10052,9 @@
       <c r="F35" s="22" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -9892,6 +10065,9 @@
       <c r="F36" s="22" t="n"/>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -9902,6 +10078,9 @@
       <c r="F37" s="22" t="n"/>
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -9912,6 +10091,9 @@
       <c r="F38" s="22" t="n"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -9922,6 +10104,9 @@
       <c r="F39" s="22" t="n"/>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -9932,6 +10117,9 @@
       <c r="F40" s="22" t="n"/>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -9942,6 +10130,9 @@
       <c r="F41" s="22" t="n"/>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -9952,6 +10143,9 @@
       <c r="F42" s="22" t="n"/>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -9962,6 +10156,9 @@
       <c r="F43" s="22" t="n"/>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -9972,6 +10169,9 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -9982,6 +10182,9 @@
       <c r="F45" s="22" t="n"/>
       <c r="G45" s="6" t="n"/>
       <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -9992,6 +10195,9 @@
       <c r="F46" s="22" t="n"/>
       <c r="G46" s="6" t="n"/>
       <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -10002,6 +10208,9 @@
       <c r="F47" s="22" t="n"/>
       <c r="G47" s="6" t="n"/>
       <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n"/>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -10012,6 +10221,9 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="6" t="n"/>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -10022,6 +10234,9 @@
       <c r="F49" s="22" t="n"/>
       <c r="G49" s="6" t="n"/>
       <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -10032,6 +10247,9 @@
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -10042,6 +10260,9 @@
       <c r="F51" s="22" t="n"/>
       <c r="G51" s="6" t="n"/>
       <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -10052,6 +10273,9 @@
       <c r="F52" s="22" t="n"/>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -10062,6 +10286,9 @@
       <c r="F53" s="22" t="n"/>
       <c r="G53" s="6" t="n"/>
       <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -10072,6 +10299,9 @@
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="6" t="n"/>
       <c r="H54" s="6" t="n"/>
+      <c r="I54" s="6" t="n"/>
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -10082,6 +10312,9 @@
       <c r="F55" s="22" t="n"/>
       <c r="G55" s="6" t="n"/>
       <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="n"/>
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -10092,6 +10325,9 @@
       <c r="F56" s="22" t="n"/>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="6" t="n"/>
+      <c r="I56" s="6" t="n"/>
+      <c r="J56" s="6" t="n"/>
+      <c r="K56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -10102,6 +10338,9 @@
       <c r="F57" s="22" t="n"/>
       <c r="G57" s="6" t="n"/>
       <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="n"/>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -10112,6 +10351,9 @@
       <c r="F58" s="22" t="n"/>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="n"/>
+      <c r="J58" s="6" t="n"/>
+      <c r="K58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -10122,6 +10364,9 @@
       <c r="F59" s="22" t="n"/>
       <c r="G59" s="6" t="n"/>
       <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="n"/>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="E60" s="24" t="n"/>
@@ -13888,7 +14133,7 @@
       <c r="F1000" s="24" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." type="list">
       <formula1>=Days</formula1>
     </dataValidation>
@@ -13899,6 +14144,9 @@
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Enter a date" error="Enter a date, for example 2026-12-12." type="date" operator="between">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2040,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." type="list">
+      <formula1>=Repeats</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13913,7 +14161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U1000"/>
+  <dimension ref="A1:W1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13937,6 +14185,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -14043,6 +14293,16 @@
       <c r="U1" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="V1" s="10" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="W1" s="10" t="inlineStr">
+        <is>
+          <t>Uniform color</t>
         </is>
       </c>
     </row>
@@ -14120,6 +14380,8 @@
           <t>Schedules post the Wednesday before.</t>
         </is>
       </c>
+      <c r="V2" s="11" t="inlineStr"/>
+      <c r="W2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -14195,6 +14457,8 @@
           <t>Arrive 45 minutes early.</t>
         </is>
       </c>
+      <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -14246,6 +14510,8 @@
         <v>46330</v>
       </c>
       <c r="U4" s="6" t="inlineStr"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -14279,29 +14545,63 @@
       <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="22" t="n"/>
       <c r="U5" s="6" t="inlineStr"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="22" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Extra serving practice</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>46368</v>
+      </c>
       <c r="D6" s="22" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Test Gym</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr"/>
       <c r="O6" s="22" t="n"/>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n"/>
-      <c r="S6" s="6" t="n"/>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr"/>
       <c r="T6" s="22" t="n"/>
-      <c r="U6" s="6" t="n"/>
+      <c r="U6" s="6" t="inlineStr"/>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -14325,6 +14625,8 @@
       <c r="S7" s="6" t="n"/>
       <c r="T7" s="22" t="n"/>
       <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -14348,6 +14650,8 @@
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="22" t="n"/>
       <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -14371,6 +14675,8 @@
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="22" t="n"/>
       <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -14394,6 +14700,8 @@
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="22" t="n"/>
       <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -14417,6 +14725,8 @@
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="22" t="n"/>
       <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -14440,6 +14750,8 @@
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="22" t="n"/>
       <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -14463,6 +14775,8 @@
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="22" t="n"/>
       <c r="U13" s="6" t="n"/>
+      <c r="V13" s="6" t="n"/>
+      <c r="W13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -14486,6 +14800,8 @@
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="22" t="n"/>
       <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -14509,6 +14825,8 @@
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="22" t="n"/>
       <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -14532,6 +14850,8 @@
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="22" t="n"/>
       <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -14555,6 +14875,8 @@
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="22" t="n"/>
       <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -14578,6 +14900,8 @@
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="22" t="n"/>
       <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -14601,6 +14925,8 @@
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="22" t="n"/>
       <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -14624,6 +14950,8 @@
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="22" t="n"/>
       <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -14647,6 +14975,8 @@
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="22" t="n"/>
       <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -14670,6 +15000,8 @@
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="22" t="n"/>
       <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -14693,6 +15025,8 @@
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="22" t="n"/>
       <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -14716,6 +15050,8 @@
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="22" t="n"/>
       <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -14739,6 +15075,8 @@
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="22" t="n"/>
       <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -14762,6 +15100,8 @@
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="22" t="n"/>
       <c r="U26" s="6" t="n"/>
+      <c r="V26" s="6" t="n"/>
+      <c r="W26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -14785,6 +15125,8 @@
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="22" t="n"/>
       <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -14808,6 +15150,8 @@
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="22" t="n"/>
       <c r="U28" s="6" t="n"/>
+      <c r="V28" s="6" t="n"/>
+      <c r="W28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -14831,6 +15175,8 @@
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="22" t="n"/>
       <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -14854,6 +15200,8 @@
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="22" t="n"/>
       <c r="U30" s="6" t="n"/>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -14877,6 +15225,8 @@
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="22" t="n"/>
       <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -14900,6 +15250,8 @@
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="22" t="n"/>
       <c r="U32" s="6" t="n"/>
+      <c r="V32" s="6" t="n"/>
+      <c r="W32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -14923,6 +15275,8 @@
       <c r="S33" s="6" t="n"/>
       <c r="T33" s="22" t="n"/>
       <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -14946,6 +15300,8 @@
       <c r="S34" s="6" t="n"/>
       <c r="T34" s="22" t="n"/>
       <c r="U34" s="6" t="n"/>
+      <c r="V34" s="6" t="n"/>
+      <c r="W34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -14969,6 +15325,8 @@
       <c r="S35" s="6" t="n"/>
       <c r="T35" s="22" t="n"/>
       <c r="U35" s="6" t="n"/>
+      <c r="V35" s="6" t="n"/>
+      <c r="W35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -14992,6 +15350,8 @@
       <c r="S36" s="6" t="n"/>
       <c r="T36" s="22" t="n"/>
       <c r="U36" s="6" t="n"/>
+      <c r="V36" s="6" t="n"/>
+      <c r="W36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -15015,6 +15375,8 @@
       <c r="S37" s="6" t="n"/>
       <c r="T37" s="22" t="n"/>
       <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -15038,6 +15400,8 @@
       <c r="S38" s="6" t="n"/>
       <c r="T38" s="22" t="n"/>
       <c r="U38" s="6" t="n"/>
+      <c r="V38" s="6" t="n"/>
+      <c r="W38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -15061,6 +15425,8 @@
       <c r="S39" s="6" t="n"/>
       <c r="T39" s="22" t="n"/>
       <c r="U39" s="6" t="n"/>
+      <c r="V39" s="6" t="n"/>
+      <c r="W39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -15084,6 +15450,8 @@
       <c r="S40" s="6" t="n"/>
       <c r="T40" s="22" t="n"/>
       <c r="U40" s="6" t="n"/>
+      <c r="V40" s="6" t="n"/>
+      <c r="W40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -15107,6 +15475,8 @@
       <c r="S41" s="6" t="n"/>
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -15130,6 +15500,8 @@
       <c r="S42" s="6" t="n"/>
       <c r="T42" s="22" t="n"/>
       <c r="U42" s="6" t="n"/>
+      <c r="V42" s="6" t="n"/>
+      <c r="W42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -15153,6 +15525,8 @@
       <c r="S43" s="6" t="n"/>
       <c r="T43" s="22" t="n"/>
       <c r="U43" s="6" t="n"/>
+      <c r="V43" s="6" t="n"/>
+      <c r="W43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -15176,6 +15550,8 @@
       <c r="S44" s="6" t="n"/>
       <c r="T44" s="22" t="n"/>
       <c r="U44" s="6" t="n"/>
+      <c r="V44" s="6" t="n"/>
+      <c r="W44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -15199,6 +15575,8 @@
       <c r="S45" s="6" t="n"/>
       <c r="T45" s="22" t="n"/>
       <c r="U45" s="6" t="n"/>
+      <c r="V45" s="6" t="n"/>
+      <c r="W45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -15222,6 +15600,8 @@
       <c r="S46" s="6" t="n"/>
       <c r="T46" s="22" t="n"/>
       <c r="U46" s="6" t="n"/>
+      <c r="V46" s="6" t="n"/>
+      <c r="W46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -15245,6 +15625,8 @@
       <c r="S47" s="6" t="n"/>
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="6" t="n"/>
+      <c r="V47" s="6" t="n"/>
+      <c r="W47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -15268,6 +15650,8 @@
       <c r="S48" s="6" t="n"/>
       <c r="T48" s="22" t="n"/>
       <c r="U48" s="6" t="n"/>
+      <c r="V48" s="6" t="n"/>
+      <c r="W48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -15291,6 +15675,8 @@
       <c r="S49" s="6" t="n"/>
       <c r="T49" s="22" t="n"/>
       <c r="U49" s="6" t="n"/>
+      <c r="V49" s="6" t="n"/>
+      <c r="W49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -15314,6 +15700,8 @@
       <c r="S50" s="6" t="n"/>
       <c r="T50" s="22" t="n"/>
       <c r="U50" s="6" t="n"/>
+      <c r="V50" s="6" t="n"/>
+      <c r="W50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -15337,6 +15725,8 @@
       <c r="S51" s="6" t="n"/>
       <c r="T51" s="22" t="n"/>
       <c r="U51" s="6" t="n"/>
+      <c r="V51" s="6" t="n"/>
+      <c r="W51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -15360,6 +15750,8 @@
       <c r="S52" s="6" t="n"/>
       <c r="T52" s="22" t="n"/>
       <c r="U52" s="6" t="n"/>
+      <c r="V52" s="6" t="n"/>
+      <c r="W52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -15383,6 +15775,8 @@
       <c r="S53" s="6" t="n"/>
       <c r="T53" s="22" t="n"/>
       <c r="U53" s="6" t="n"/>
+      <c r="V53" s="6" t="n"/>
+      <c r="W53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -15406,6 +15800,8 @@
       <c r="S54" s="6" t="n"/>
       <c r="T54" s="22" t="n"/>
       <c r="U54" s="6" t="n"/>
+      <c r="V54" s="6" t="n"/>
+      <c r="W54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -15429,6 +15825,8 @@
       <c r="S55" s="6" t="n"/>
       <c r="T55" s="22" t="n"/>
       <c r="U55" s="6" t="n"/>
+      <c r="V55" s="6" t="n"/>
+      <c r="W55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -15452,6 +15850,8 @@
       <c r="S56" s="6" t="n"/>
       <c r="T56" s="22" t="n"/>
       <c r="U56" s="6" t="n"/>
+      <c r="V56" s="6" t="n"/>
+      <c r="W56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -15475,6 +15875,8 @@
       <c r="S57" s="6" t="n"/>
       <c r="T57" s="22" t="n"/>
       <c r="U57" s="6" t="n"/>
+      <c r="V57" s="6" t="n"/>
+      <c r="W57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -15498,6 +15900,8 @@
       <c r="S58" s="6" t="n"/>
       <c r="T58" s="22" t="n"/>
       <c r="U58" s="6" t="n"/>
+      <c r="V58" s="6" t="n"/>
+      <c r="W58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -15521,6 +15925,8 @@
       <c r="S59" s="6" t="n"/>
       <c r="T59" s="22" t="n"/>
       <c r="U59" s="6" t="n"/>
+      <c r="V59" s="6" t="n"/>
+      <c r="W59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="C60" s="24" t="n"/>
@@ -21276,12 +21682,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -21571,7 +21993,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Tournament</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -21618,7 +22040,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Tournament</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -21660,7 +22082,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -21671,6 +22093,11 @@
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Youth L</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -21690,6 +22117,11 @@
           <t>Wednesday</t>
         </is>
       </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Every 3 weeks</t>
@@ -21698,6 +22130,11 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Youth XL</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Practice uniform colors</t>
         </is>
       </c>
     </row>

--- a/api/test/import/team-sample.xlsx
+++ b/api/test/import/team-sample.xlsx
@@ -393,6 +393,11 @@
         <t>Practice uniform color. New colors are added to the team's list.</t>
       </text>
     </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Street address. Families get a map link; without one the map searches the location.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -441,6 +446,16 @@
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>Practices only.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Street address of the venue. Families get a map link; without one the map searches the venue and city.</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>Travel tournaments: the team hotel's street address.</t>
       </text>
     </comment>
   </commentList>
@@ -9439,7 +9454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9453,6 +9468,7 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -9511,6 +9527,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -9564,6 +9585,11 @@
           <t>Bring both jerseys</t>
         </is>
       </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>1234 Example Rd, Roswell, GA 30076</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -9607,6 +9633,11 @@
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>1 Gym Way, Roswell, GA 30076</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -9652,6 +9683,7 @@
           <t>Both jerseys</t>
         </is>
       </c>
+      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -9665,6 +9697,7 @@
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -9678,6 +9711,7 @@
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -9691,6 +9725,7 @@
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -9704,6 +9739,7 @@
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -9717,6 +9753,7 @@
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -9730,6 +9767,7 @@
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -9743,6 +9781,7 @@
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -9756,6 +9795,7 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -9769,6 +9809,7 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -9782,6 +9823,7 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -9795,6 +9837,7 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -9808,6 +9851,7 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9821,6 +9865,7 @@
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -9834,6 +9879,7 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -9847,6 +9893,7 @@
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -9860,6 +9907,7 @@
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9873,6 +9921,7 @@
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -9886,6 +9935,7 @@
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -9899,6 +9949,7 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -9912,6 +9963,7 @@
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -9925,6 +9977,7 @@
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -9938,6 +9991,7 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -9951,6 +10005,7 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -9964,6 +10019,7 @@
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -9977,6 +10033,7 @@
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -9990,6 +10047,7 @@
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -10003,6 +10061,7 @@
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -10016,6 +10075,7 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -10029,6 +10089,7 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -10042,6 +10103,7 @@
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -10055,6 +10117,7 @@
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -10068,6 +10131,7 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -10081,6 +10145,7 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -10094,6 +10159,7 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -10107,6 +10173,7 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -10120,6 +10187,7 @@
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -10133,6 +10201,7 @@
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -10146,6 +10215,7 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -10159,6 +10229,7 @@
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -10172,6 +10243,7 @@
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
+      <c r="L44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -10185,6 +10257,7 @@
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
+      <c r="L45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -10198,6 +10271,7 @@
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
+      <c r="L46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -10211,6 +10285,7 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -10224,6 +10299,7 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -10237,6 +10313,7 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -10250,6 +10327,7 @@
       <c r="I50" s="6" t="n"/>
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -10263,6 +10341,7 @@
       <c r="I51" s="6" t="n"/>
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -10276,6 +10355,7 @@
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -10289,6 +10369,7 @@
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -10302,6 +10383,7 @@
       <c r="I54" s="6" t="n"/>
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="6" t="n"/>
+      <c r="L54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -10315,6 +10397,7 @@
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
+      <c r="L55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -10328,6 +10411,7 @@
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="6" t="n"/>
+      <c r="L56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -10341,6 +10425,7 @@
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
+      <c r="L57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -10354,6 +10439,7 @@
       <c r="I58" s="6" t="n"/>
       <c r="J58" s="6" t="n"/>
       <c r="K58" s="6" t="n"/>
+      <c r="L58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -10367,6 +10453,7 @@
       <c r="I59" s="6" t="n"/>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
+      <c r="L59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="E60" s="24" t="n"/>
@@ -14161,7 +14248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W1000"/>
+  <dimension ref="A1:Y1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14187,6 +14274,8 @@
     <col width="36" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -14303,6 +14392,16 @@
       <c r="W1" s="10" t="inlineStr">
         <is>
           <t>Uniform color</t>
+        </is>
+      </c>
+      <c r="X1" s="10" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="Y1" s="10" t="inlineStr">
+        <is>
+          <t>Hotel address</t>
         </is>
       </c>
     </row>
@@ -14382,6 +14481,12 @@
       </c>
       <c r="V2" s="11" t="inlineStr"/>
       <c r="W2" s="11" t="inlineStr"/>
+      <c r="X2" s="11" t="inlineStr">
+        <is>
+          <t>285 Andrew Young International Blvd NW, Atlanta, GA 30313</t>
+        </is>
+      </c>
+      <c r="Y2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -14431,7 +14536,11 @@
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr"/>
-      <c r="L3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Peach Inn</t>
+        </is>
+      </c>
       <c r="M3" s="6" t="inlineStr"/>
       <c r="N3" s="6" t="inlineStr"/>
       <c r="O3" s="22" t="n"/>
@@ -14457,8 +14566,18 @@
           <t>Arrive 45 minutes early.</t>
         </is>
       </c>
-      <c r="V3" s="6" t="n"/>
-      <c r="W3" s="6" t="n"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>100 Expo Dr, Atlanta, GA 30303</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>5 Hotel Row, Atlanta, GA 30303</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -14512,6 +14631,8 @@
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="n"/>
       <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -14547,6 +14668,8 @@
       <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="n"/>
       <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -14602,6 +14725,12 @@
           <t>White</t>
         </is>
       </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>1 Gym Way, Roswell, GA 30076</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -14627,6 +14756,8 @@
       <c r="U7" s="6" t="n"/>
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -14652,6 +14783,8 @@
       <c r="U8" s="6" t="n"/>
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -14677,6 +14810,8 @@
       <c r="U9" s="6" t="n"/>
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
+      <c r="X9" s="6" t="n"/>
+      <c r="Y9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -14702,6 +14837,8 @@
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="n"/>
+      <c r="Y10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -14727,6 +14864,8 @@
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -14752,6 +14891,8 @@
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -14777,6 +14918,8 @@
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -14802,6 +14945,8 @@
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -14827,6 +14972,8 @@
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -14852,6 +14999,8 @@
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -14877,6 +15026,8 @@
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -14902,6 +15053,8 @@
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -14927,6 +15080,8 @@
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -14952,6 +15107,8 @@
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -14977,6 +15134,8 @@
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -15002,6 +15161,8 @@
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -15027,6 +15188,8 @@
       <c r="U23" s="6" t="n"/>
       <c r="V23" s="6" t="n"/>
       <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -15052,6 +15215,8 @@
       <c r="U24" s="6" t="n"/>
       <c r="V24" s="6" t="n"/>
       <c r="W24" s="6" t="n"/>
+      <c r="X24" s="6" t="n"/>
+      <c r="Y24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -15077,6 +15242,8 @@
       <c r="U25" s="6" t="n"/>
       <c r="V25" s="6" t="n"/>
       <c r="W25" s="6" t="n"/>
+      <c r="X25" s="6" t="n"/>
+      <c r="Y25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -15102,6 +15269,8 @@
       <c r="U26" s="6" t="n"/>
       <c r="V26" s="6" t="n"/>
       <c r="W26" s="6" t="n"/>
+      <c r="X26" s="6" t="n"/>
+      <c r="Y26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -15127,6 +15296,8 @@
       <c r="U27" s="6" t="n"/>
       <c r="V27" s="6" t="n"/>
       <c r="W27" s="6" t="n"/>
+      <c r="X27" s="6" t="n"/>
+      <c r="Y27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -15152,6 +15323,8 @@
       <c r="U28" s="6" t="n"/>
       <c r="V28" s="6" t="n"/>
       <c r="W28" s="6" t="n"/>
+      <c r="X28" s="6" t="n"/>
+      <c r="Y28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -15177,6 +15350,8 @@
       <c r="U29" s="6" t="n"/>
       <c r="V29" s="6" t="n"/>
       <c r="W29" s="6" t="n"/>
+      <c r="X29" s="6" t="n"/>
+      <c r="Y29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -15202,6 +15377,8 @@
       <c r="U30" s="6" t="n"/>
       <c r="V30" s="6" t="n"/>
       <c r="W30" s="6" t="n"/>
+      <c r="X30" s="6" t="n"/>
+      <c r="Y30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -15227,6 +15404,8 @@
       <c r="U31" s="6" t="n"/>
       <c r="V31" s="6" t="n"/>
       <c r="W31" s="6" t="n"/>
+      <c r="X31" s="6" t="n"/>
+      <c r="Y31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -15252,6 +15431,8 @@
       <c r="U32" s="6" t="n"/>
       <c r="V32" s="6" t="n"/>
       <c r="W32" s="6" t="n"/>
+      <c r="X32" s="6" t="n"/>
+      <c r="Y32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -15277,6 +15458,8 @@
       <c r="U33" s="6" t="n"/>
       <c r="V33" s="6" t="n"/>
       <c r="W33" s="6" t="n"/>
+      <c r="X33" s="6" t="n"/>
+      <c r="Y33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -15302,6 +15485,8 @@
       <c r="U34" s="6" t="n"/>
       <c r="V34" s="6" t="n"/>
       <c r="W34" s="6" t="n"/>
+      <c r="X34" s="6" t="n"/>
+      <c r="Y34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -15327,6 +15512,8 @@
       <c r="U35" s="6" t="n"/>
       <c r="V35" s="6" t="n"/>
       <c r="W35" s="6" t="n"/>
+      <c r="X35" s="6" t="n"/>
+      <c r="Y35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -15352,6 +15539,8 @@
       <c r="U36" s="6" t="n"/>
       <c r="V36" s="6" t="n"/>
       <c r="W36" s="6" t="n"/>
+      <c r="X36" s="6" t="n"/>
+      <c r="Y36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -15377,6 +15566,8 @@
       <c r="U37" s="6" t="n"/>
       <c r="V37" s="6" t="n"/>
       <c r="W37" s="6" t="n"/>
+      <c r="X37" s="6" t="n"/>
+      <c r="Y37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -15402,6 +15593,8 @@
       <c r="U38" s="6" t="n"/>
       <c r="V38" s="6" t="n"/>
       <c r="W38" s="6" t="n"/>
+      <c r="X38" s="6" t="n"/>
+      <c r="Y38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -15427,6 +15620,8 @@
       <c r="U39" s="6" t="n"/>
       <c r="V39" s="6" t="n"/>
       <c r="W39" s="6" t="n"/>
+      <c r="X39" s="6" t="n"/>
+      <c r="Y39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -15452,6 +15647,8 @@
       <c r="U40" s="6" t="n"/>
       <c r="V40" s="6" t="n"/>
       <c r="W40" s="6" t="n"/>
+      <c r="X40" s="6" t="n"/>
+      <c r="Y40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -15477,6 +15674,8 @@
       <c r="U41" s="6" t="n"/>
       <c r="V41" s="6" t="n"/>
       <c r="W41" s="6" t="n"/>
+      <c r="X41" s="6" t="n"/>
+      <c r="Y41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -15502,6 +15701,8 @@
       <c r="U42" s="6" t="n"/>
       <c r="V42" s="6" t="n"/>
       <c r="W42" s="6" t="n"/>
+      <c r="X42" s="6" t="n"/>
+      <c r="Y42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -15527,6 +15728,8 @@
       <c r="U43" s="6" t="n"/>
       <c r="V43" s="6" t="n"/>
       <c r="W43" s="6" t="n"/>
+      <c r="X43" s="6" t="n"/>
+      <c r="Y43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -15552,6 +15755,8 @@
       <c r="U44" s="6" t="n"/>
       <c r="V44" s="6" t="n"/>
       <c r="W44" s="6" t="n"/>
+      <c r="X44" s="6" t="n"/>
+      <c r="Y44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -15577,6 +15782,8 @@
       <c r="U45" s="6" t="n"/>
       <c r="V45" s="6" t="n"/>
       <c r="W45" s="6" t="n"/>
+      <c r="X45" s="6" t="n"/>
+      <c r="Y45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -15602,6 +15809,8 @@
       <c r="U46" s="6" t="n"/>
       <c r="V46" s="6" t="n"/>
       <c r="W46" s="6" t="n"/>
+      <c r="X46" s="6" t="n"/>
+      <c r="Y46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -15627,6 +15836,8 @@
       <c r="U47" s="6" t="n"/>
       <c r="V47" s="6" t="n"/>
       <c r="W47" s="6" t="n"/>
+      <c r="X47" s="6" t="n"/>
+      <c r="Y47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -15652,6 +15863,8 @@
       <c r="U48" s="6" t="n"/>
       <c r="V48" s="6" t="n"/>
       <c r="W48" s="6" t="n"/>
+      <c r="X48" s="6" t="n"/>
+      <c r="Y48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -15677,6 +15890,8 @@
       <c r="U49" s="6" t="n"/>
       <c r="V49" s="6" t="n"/>
       <c r="W49" s="6" t="n"/>
+      <c r="X49" s="6" t="n"/>
+      <c r="Y49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -15702,6 +15917,8 @@
       <c r="U50" s="6" t="n"/>
       <c r="V50" s="6" t="n"/>
       <c r="W50" s="6" t="n"/>
+      <c r="X50" s="6" t="n"/>
+      <c r="Y50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -15727,6 +15944,8 @@
       <c r="U51" s="6" t="n"/>
       <c r="V51" s="6" t="n"/>
       <c r="W51" s="6" t="n"/>
+      <c r="X51" s="6" t="n"/>
+      <c r="Y51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -15752,6 +15971,8 @@
       <c r="U52" s="6" t="n"/>
       <c r="V52" s="6" t="n"/>
       <c r="W52" s="6" t="n"/>
+      <c r="X52" s="6" t="n"/>
+      <c r="Y52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -15777,6 +15998,8 @@
       <c r="U53" s="6" t="n"/>
       <c r="V53" s="6" t="n"/>
       <c r="W53" s="6" t="n"/>
+      <c r="X53" s="6" t="n"/>
+      <c r="Y53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -15802,6 +16025,8 @@
       <c r="U54" s="6" t="n"/>
       <c r="V54" s="6" t="n"/>
       <c r="W54" s="6" t="n"/>
+      <c r="X54" s="6" t="n"/>
+      <c r="Y54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -15827,6 +16052,8 @@
       <c r="U55" s="6" t="n"/>
       <c r="V55" s="6" t="n"/>
       <c r="W55" s="6" t="n"/>
+      <c r="X55" s="6" t="n"/>
+      <c r="Y55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -15852,6 +16079,8 @@
       <c r="U56" s="6" t="n"/>
       <c r="V56" s="6" t="n"/>
       <c r="W56" s="6" t="n"/>
+      <c r="X56" s="6" t="n"/>
+      <c r="Y56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -15877,6 +16106,8 @@
       <c r="U57" s="6" t="n"/>
       <c r="V57" s="6" t="n"/>
       <c r="W57" s="6" t="n"/>
+      <c r="X57" s="6" t="n"/>
+      <c r="Y57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -15902,6 +16133,8 @@
       <c r="U58" s="6" t="n"/>
       <c r="V58" s="6" t="n"/>
       <c r="W58" s="6" t="n"/>
+      <c r="X58" s="6" t="n"/>
+      <c r="Y58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -15927,6 +16160,8 @@
       <c r="U59" s="6" t="n"/>
       <c r="V59" s="6" t="n"/>
       <c r="W59" s="6" t="n"/>
+      <c r="X59" s="6" t="n"/>
+      <c r="Y59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="C60" s="24" t="n"/>
